--- a/src/test/resources/testdata/testsData.xlsx
+++ b/src/test/resources/testdata/testsData.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="17">
   <si>
     <t>Test Case</t>
   </si>

--- a/src/test/resources/testdata/testsData.xlsx
+++ b/src/test/resources/testdata/testsData.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="17">
   <si>
     <t>Test Case</t>
   </si>

--- a/src/test/resources/testdata/testsData.xlsx
+++ b/src/test/resources/testdata/testsData.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="17">
   <si>
     <t>Test Case</t>
   </si>

--- a/src/test/resources/testdata/testsData.xlsx
+++ b/src/test/resources/testdata/testsData.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="17">
   <si>
     <t>Test Case</t>
   </si>

--- a/src/test/resources/testdata/testsData.xlsx
+++ b/src/test/resources/testdata/testsData.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="17">
   <si>
     <t>Test Case</t>
   </si>

--- a/src/test/resources/testdata/testsData.xlsx
+++ b/src/test/resources/testdata/testsData.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="17">
   <si>
     <t>Test Case</t>
   </si>

--- a/src/test/resources/testdata/testsData.xlsx
+++ b/src/test/resources/testdata/testsData.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="17">
   <si>
     <t>Test Case</t>
   </si>
